--- a/product_selector_out/STM32F2 series.xlsx
+++ b/product_selector_out/STM32F2 series.xlsx
@@ -27371,7 +27371,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -27635,7 +27635,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -27899,7 +27899,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -27987,7 +27987,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28075,7 +28075,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28163,7 +28163,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28251,7 +28251,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28339,7 +28339,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28603,7 +28603,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28691,7 +28691,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28779,7 +28779,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -29395,7 +29395,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -29483,7 +29483,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -29571,7 +29571,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F2 series.xlsx
+++ b/product_selector_out/STM32F2 series.xlsx
@@ -14518,14 +14518,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
@@ -14533,9 +14533,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
@@ -14855,14 +14855,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
@@ -14870,9 +14870,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q13" s="10" t="inlineStr">
@@ -15192,14 +15192,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
@@ -15207,9 +15207,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q14" s="10" t="inlineStr">
@@ -15529,14 +15529,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
@@ -15544,9 +15544,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
@@ -15866,14 +15866,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -15881,9 +15881,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
@@ -16203,14 +16203,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
@@ -16218,9 +16218,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
@@ -16540,14 +16540,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
@@ -16555,9 +16555,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
@@ -16877,14 +16877,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
@@ -16892,9 +16892,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
@@ -17214,14 +17214,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
@@ -17229,9 +17229,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q20" s="10" t="inlineStr">
@@ -17551,14 +17551,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
@@ -17566,9 +17566,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
@@ -17888,14 +17888,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
@@ -17903,9 +17903,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q22" s="10" t="inlineStr">
@@ -18225,14 +18225,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
@@ -18240,9 +18240,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q23" s="10" t="inlineStr">
@@ -18562,14 +18562,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
@@ -18577,9 +18577,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q24" s="10" t="inlineStr">
@@ -18899,14 +18899,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
@@ -18914,9 +18914,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr">
@@ -19236,14 +19236,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
@@ -19251,9 +19251,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q26" s="10" t="inlineStr">
@@ -19573,14 +19573,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
@@ -19588,9 +19588,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q27" s="10" t="inlineStr">
@@ -19910,14 +19910,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -19925,9 +19925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q28" s="10" t="inlineStr">
@@ -20247,14 +20247,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
@@ -20262,9 +20262,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr">
@@ -20584,14 +20584,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
@@ -20599,9 +20599,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q30" s="10" t="inlineStr">
@@ -20921,14 +20921,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
@@ -20936,9 +20936,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr">
@@ -21258,14 +21258,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
@@ -21273,9 +21273,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
@@ -21595,14 +21595,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -21610,9 +21610,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr">
@@ -21932,14 +21932,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -21947,9 +21947,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q34" s="10" t="inlineStr">
@@ -22269,14 +22269,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -22284,9 +22284,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q35" s="10" t="inlineStr">
@@ -22606,14 +22606,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr">
@@ -22621,9 +22621,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q36" s="10" t="inlineStr">
@@ -22943,14 +22943,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
@@ -22958,9 +22958,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q37" s="10" t="inlineStr">
@@ -23280,14 +23280,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
@@ -23295,9 +23295,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q38" s="10" t="inlineStr">
@@ -23617,14 +23617,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -23632,9 +23632,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q39" s="10" t="inlineStr">
@@ -23954,14 +23954,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr">
@@ -23969,9 +23969,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q40" s="10" t="inlineStr">
@@ -24291,14 +24291,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -24306,9 +24306,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q41" s="10" t="inlineStr">
@@ -24628,14 +24628,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
@@ -24643,9 +24643,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q42" s="10" t="inlineStr">
@@ -24965,14 +24965,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
@@ -24980,9 +24980,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q43" s="10" t="inlineStr">
@@ -25302,14 +25302,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr">
@@ -25317,9 +25317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q44" s="10" t="inlineStr">
@@ -25639,14 +25639,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr">
@@ -25654,9 +25654,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q45" s="10" t="inlineStr">
@@ -25976,14 +25976,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O46" s="6" t="inlineStr">
@@ -25991,9 +25991,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q46" s="10" t="inlineStr">
@@ -26313,14 +26313,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr">
@@ -26328,9 +26328,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q47" s="10" t="inlineStr">
@@ -26650,14 +26650,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O48" s="6" t="inlineStr">
@@ -26665,9 +26665,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q48" s="10" t="inlineStr">
@@ -26987,14 +26987,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O49" s="6" t="inlineStr">
@@ -27002,9 +27002,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q49" s="10" t="inlineStr">

--- a/product_selector_out/STM32F2 series.xlsx
+++ b/product_selector_out/STM32F2 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO49"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.52734375" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="18" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -917,6 +918,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1014,6 +1020,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1348,6 +1355,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -1685,6 +1697,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -2022,6 +2039,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -2359,6 +2381,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -2696,6 +2723,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -3033,6 +3065,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -3370,6 +3407,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -3707,6 +3749,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -4044,6 +4091,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -4381,6 +4433,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -4718,6 +4775,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -5055,6 +5117,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -5392,6 +5459,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -5729,6 +5801,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -6066,6 +6143,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -6403,6 +6485,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -6740,6 +6827,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -7077,6 +7169,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -7414,6 +7511,11 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -7751,6 +7853,11 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -8088,6 +8195,11 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -8425,6 +8537,11 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -8762,6 +8879,11 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -9099,6 +9221,11 @@
       </c>
       <c r="BO35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -9436,6 +9563,11 @@
       </c>
       <c r="BO36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -9773,6 +9905,11 @@
       </c>
       <c r="BO37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -10110,6 +10247,11 @@
       </c>
       <c r="BO38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -10447,6 +10589,11 @@
       </c>
       <c r="BO39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -10784,6 +10931,11 @@
       </c>
       <c r="BO40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -11121,6 +11273,11 @@
       </c>
       <c r="BO41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -11458,6 +11615,11 @@
       </c>
       <c r="BO42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -11795,6 +11957,11 @@
       </c>
       <c r="BO43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -12132,6 +12299,11 @@
       </c>
       <c r="BO44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -12469,6 +12641,11 @@
       </c>
       <c r="BO45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -12806,6 +12983,11 @@
       </c>
       <c r="BO46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -13143,6 +13325,11 @@
       </c>
       <c r="BO47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -13480,6 +13667,11 @@
       </c>
       <c r="BO48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -13817,12 +14009,17 @@
       </c>
       <c r="BO49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AD10:AD11"/>
     <mergeCell ref="BL10:BL11"/>
@@ -13843,13 +14040,15 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="M10:N10"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="O10"/>
     <mergeCell ref="AC10:AC11"/>
@@ -13867,9 +14066,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="U10:U11"/>
@@ -13942,7 +14140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO49"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14012,6 +14210,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14359,6 +14558,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -14456,6 +14660,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14788,7 +14993,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15125,7 +15335,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15462,7 +15677,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15799,7 +16019,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16136,7 +16361,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16473,7 +16703,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16810,7 +17045,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17147,7 +17387,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17484,7 +17729,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17821,7 +18071,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18158,7 +18413,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18495,7 +18755,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18832,7 +19097,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19169,7 +19439,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19506,7 +19781,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19843,7 +20123,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20180,7 +20465,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20517,7 +20807,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20854,7 +21149,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21191,7 +21491,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
+      <c r="BO31" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21528,7 +21833,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO32" s="6" t="inlineStr">
+      <c r="BO32" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21865,7 +22175,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO33" s="6" t="inlineStr">
+      <c r="BO33" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22202,7 +22517,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO34" s="6" t="inlineStr">
+      <c r="BO34" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22539,7 +22859,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO35" s="6" t="inlineStr">
+      <c r="BO35" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22876,7 +23201,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO36" s="6" t="inlineStr">
+      <c r="BO36" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23213,7 +23543,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO37" s="6" t="inlineStr">
+      <c r="BO37" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23550,7 +23885,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO38" s="6" t="inlineStr">
+      <c r="BO38" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23887,7 +24227,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO39" s="6" t="inlineStr">
+      <c r="BO39" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24224,7 +24569,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO40" s="6" t="inlineStr">
+      <c r="BO40" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24561,7 +24911,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO41" s="6" t="inlineStr">
+      <c r="BO41" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24898,7 +25253,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO42" s="6" t="inlineStr">
+      <c r="BO42" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25235,7 +25595,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO43" s="6" t="inlineStr">
+      <c r="BO43" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25572,7 +25937,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO44" s="6" t="inlineStr">
+      <c r="BO44" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25909,7 +26279,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO45" s="6" t="inlineStr">
+      <c r="BO45" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26246,7 +26621,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO46" s="6" t="inlineStr">
+      <c r="BO46" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26583,7 +26963,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO47" s="6" t="inlineStr">
+      <c r="BO47" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26920,7 +27305,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO48" s="6" t="inlineStr">
+      <c r="BO48" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27257,7 +27647,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO49" s="6" t="inlineStr">
+      <c r="BO49" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27265,8 +27660,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
